--- a/pinlei.xlsx
+++ b/pinlei.xlsx
@@ -364,12 +364,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>鞋子品类含休闲、运动、正装、户外等多样款式，采用透气网布、软底、真皮等舒适材质，适配日常通勤、健身、商务等场景，品质可靠，满足不同穿搭需求。</t>
+          <t>各类时尚鞋款，涵盖运动鞋、休闲鞋、高跟鞋、帆布鞋等，适配日常通勤、运动健身、约会穿搭等场景，舒适耐磨又百搭，满足海外用户多元鞋履需求。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Versatile Shoes | Comfortable Footwear for Men &amp; Women. Shop premium sneakers, casual shoes, sandals &amp; dress shoes—crafted with top materials &amp; meticulous details, blending fashion &amp; function for daily, sports &amp; special occasions.</t>
+          <t>Fashion Shoes: Featuring sneakers, casual shoes, high heels, canvas shoes &amp; more. Suits daily commute, sports, fitness &amp; date outfits. Comfortable, durable &amp; versatile to meet global users’ diverse footwear needs.</t>
         </is>
       </c>
     </row>
@@ -386,12 +386,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T恤 - 时尚百搭必备单品！精选100%纯棉面料，舒适透气，多款颜色与尺码可选。提供男女款及儿童T恤，简约设计、印花图案等多种风格。快时尚潮流，性价比超高！立即选购，打造专属休闲穿搭。</t>
+          <t>T恤品类，含纯棉圆领/V领休闲款，适配日常通勤、运动健身；纯色/印花可选，透气舒适。海外用户常搜“cotton t-shirts”“casual tees”对应品类，满足多元穿搭需求。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T-Shirts - 100% cotton, comfortable &amp; breathable. Men's, women's &amp; kids' styles. Simple designs &amp; prints. Fast fashion, affordable. Shop now for casual outfits!</t>
+          <t>Cotton T-Shirts &amp; Casual Tees: Crew Neck/V-Neck, Solid/Printed Options. Breathable &amp; Comfortable. Ideal for Daily Commute &amp; Gym. Versatile Styling for Diverse Outfit Needs.</t>
         </is>
       </c>
     </row>
@@ -408,12 +408,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>时尚百搭的男女款连帽卫衣，采用舒适柔软面料，适合日常休闲、运动及户外活动。多色多码可选，简约设计与个性印花款式兼备，提供春秋季保暖与叠穿搭配。快时尚新品，高性价比，全球直邮。</t>
+          <t>连帽衫（Hoodies）：含宽松oversize、修身款，有纯棉、加绒等材质，适配运动、日常通勤、校园穿搭。海外热门休闲单品，舒适百搭，满足多元场景风格需求。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unisex hoodies: Stylish, comfortable &amp; versatile. Soft fabric for casual, sports &amp; outdoor. Multiple colors/sizes. Minimalist &amp; printed designs. Perfect for layering in spring/fall. Fast fashion, affordable. Global shipping.</t>
+          <t>Hoodies: Oversize &amp; slim-fit styles available, with 100% cotton &amp; fleece-lined options. Ideal for sports, daily commuting, campus outfits. A popular overseas casual item—comfortable, versatile, fits multiple occasion needs.</t>
         </is>
       </c>
     </row>
@@ -430,12 +430,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>时尚外套系列，采用防风防水科技面料与经典设计，兼顾保暖性与潮流感。多款风格可选，包括轻便羽绒服、休闲夹克、商务风衣等，适合户外运动、都市通勤及日常穿搭。高品质工艺，细节出众，展现个性与实用主义完美结合。</t>
+          <t>夹克品类涵盖男士/女士款，含冬季保暖夹克、春秋休闲牛仔夹克、复古飞行员夹克、工装夹克、皮夹克等。适配日常通勤、户外出行，风格简约百搭，满足海外用户多元穿搭需求。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Waterproof &amp; Windproof Jackets for Men &amp; Women. Explore down coats, trench coats &amp; sport jackets. Perfect for outdoor, commute &amp; daily wear. Shop now!</t>
+          <t>Men's &amp; Women's Jackets: Winter Warm Jackets, Spring-Autumn Casual Denim Jackets, Vintage Bomber Jackets, Work Jackets, Leather Jackets. Perfect for Daily Commute &amp; Outdoor Activities. Minimalist &amp; Versatile, catering to overseas users' diverse styling needs.</t>
         </is>
       </c>
     </row>
@@ -452,12 +452,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pants品类包含休闲裤、牛仔裤、西裤等日常必备下装，采用棉、弹力纤维等舒适面料，兼顾时尚设计与实用功能，满足通勤、休闲等多元场景穿搭需求。精选优质款式，提供多种版型与尺码选择，打造经典衣橱。</t>
+          <t>涵盖休闲裤、牛仔裤、工装裤等多类型Pants，适配日常通勤、户外休闲场景，主打舒适透气、百搭耐穿，精准匹配海外用户高频搜索需求，SEO友好。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Discover versatile pants &amp; shorts for any occasion. Breathable, stretchy fabrics. Slim, straight &amp; wide-leg fits. Perfect for casual, work, or exercise. Elevate your style with up to 200+ characters.</t>
+          <t>Pants: Covers casual pants, jeans, cargo pants &amp; more. Suitable for daily commute &amp; outdoor leisure. Features comfortable, breathable, versatile &amp; durable. Aligns with overseas users’ high-frequency search demands, SEO-friendly.</t>
         </is>
       </c>
     </row>
@@ -474,12 +474,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>【Jerseys】提供专业运动 jersey 与潮流复古款式，覆盖NBA、NFL、足球等热门赛事球队。高品质面料，官方正品授权，舒适透气设计。男、女、儿童多尺寸可选，支持定制印号。全球直达，安全支付，售后无忧。立即选购专属你的 jersey！</t>
+          <t>运动球衣品类，涵盖足球、篮球、棒球等主流运动，含正版授权款与定制印号服务，适配球员训练、球迷应援，尺码覆盖成人/儿童，透气易穿脱面料，满足运动与日常穿搭需求。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Official Jerseys Store: NBA, NFL, Soccer Jerseys for Men, Women &amp; Kids. Authentic Licensed, Customizable Names &amp; Numbers. Shop Now! 🏀⚽🏈</t>
+          <t>Jerseys for Football, Basketball, Baseball &amp; More | Official Licensed &amp; Custom Name/Number Printing | For Player Training &amp; Fan Support | Adults &amp; Kids Sizes | Breathable, Easy-On Fabric | Ideal for Sports &amp; Daily Wear</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>香水，一种通过香精与酒精混合制成的液体，用于提升个人魅力与营造氛围。涵盖女士香水、男士香水、中性香水及小众沙龙香等类型，常见香调包括花香、果香、木质香与东方香调。适用于日常、职场、约会等多样场合，留香持久，是展现个性的精致选择。</t>
+          <t>香水品类含淡香水（EDT）、浓香水（EDP），适配日常通勤、约会等场景，有清新花果香、木质调等热门香调，满足海外用户对持久留香、多元风格的需求。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Perfume: A blend of fragrance oils &amp; alcohol for charm &amp; mood. Types: women's, men's, unisex, niche. Scents: floral, fruity, woody, oriental. For daily, work, date. Long-lasting. Express your style. Shop now! #Perfume</t>
+          <t>Perfume Category: Includes Eau de Toilette (EDT) &amp; Eau de Parfum (EDP). Ideal for daily commute, dates, etc. With popular notes like fresh fruity-floral &amp; woody, meeting overseas users’ needs for long-lasting scent &amp; diverse styles.</t>
         </is>
       </c>
     </row>
@@ -518,12 +518,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>电子品类提供前沿科技产品，包括智能手机、电脑、智能家居及配件，融合创新设计与高性能，为全球用户带来便捷与高效体验。探索最新电子潮流，满足生活与专业需求。</t>
+          <t>电子品类，聚焦海外用户高频搜索的消费电子、电子配件、电子零件、电子设备等，涵盖手机配件、音频设备、智能家居电子等实用商品，适配谷歌等海外搜索平台需求。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Electronics: smartphones, laptops, wearables &amp; components. Innovative tech &amp; premium quality for global customers. Explore smart living. Shop now! #Tech #Electronics</t>
+          <t>Electronic Category: Specializes in consumer electronics, accessories, components &amp; devices highly searched by overseas users. Covers practical items: phone accessories, audio gear, smart home electronics. Optimized for Google, Bing, Yahoo &amp; other overseas platforms.</t>
         </is>
       </c>
     </row>
@@ -540,188 +540,166 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>饰品配饰类产品，涵盖项链、手链、耳饰、戒指、帽子、围巾等时尚单品。精选材质，设计多样，为日常穿搭注入个性亮点，轻松提升整体造型的精致感与完整度。</t>
+          <t>时尚配饰、数码配件等各类配件，包含包包、首饰、手机壳、耳机配件、手表带等，适配海外用户日常穿搭与数码使用需求，品质可靠。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Premium Accessories: Chargers, headphones, screen protectors &amp; more. High compatibility &amp; durability for multi-brand devices. Stylish &amp; protective. Global shipping. Authentic products. Enhance your mobile life!</t>
+          <t>Accessories: Fashion &amp; digital accessories including bags, jewelry, phone cases, headphone accessories, watch bands. For overseas users' daily wear &amp; digital use, reliable quality.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Headwear</t>
+          <t>Sweaters</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>headwear</t>
+          <t>sweaters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>时尚帽饰品类，涵盖棒球帽、渔夫帽、贝雷帽及宽檐帽等多种款式，精选优质材质，兼顾防晒与搭配，为日常造型注入亮点，是提升时尚感的必备单品。</t>
+          <t>秋冬毛衣品类，涵盖圆领、开衫、高领经典款，精选羊毛、纯棉亲肤材质，适配日常通勤、休闲穿搭场景，覆盖海外用户常搜关键词，SEO友好的舒适单品分类。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Headwear Collection: baseball caps, bucket hats, berets &amp; wide-brim hats. Premium materials, UV protection &amp; stylish designs. Elevate your daily look. Shop now! 👒🧢</t>
+          <t>Fall &amp; Winter Sweaters: Classic Crew Neck, Cardigan &amp; Turtleneck Styles. Crafted from Premium Wool &amp; Skin-Friendly Pure Cotton, Ideal for Daily Commute &amp; Casual Outfits. Comfortable Pieces Aligned with Overseas Users’ Top Queries, SEO-Friendly Category.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sweaters</t>
+          <t>Hats</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweaters</t>
+          <t>hats</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>舒适保暖的针织毛衣，提供羊绒、美利奴羊毛、棉质等多种材质选择，涵盖男装、女装及儿童款式，适合日常休闲、职场通勤及户外穿搭。精选高品质面料，注重细节设计与版型剪裁，打造时尚与功能性兼具的秋冬必备单品。</t>
+          <t>帽子品类含棒球帽、渔夫帽、遮阳帽、针织帽，适配户外、日常穿搭，时尚百搭，满足休闲、运动、防晒需求，海外热门款齐全，选品丰富。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sweaters: premium wool, cashmere &amp; cotton styles for men, women &amp; kids. Perfect for casual, office &amp; outdoor wear. Shop quality knitwear now!</t>
+          <t>Hats: Baseball Caps, Fisherman Hats, Sun Hats &amp; Knit Hats. Perfect for outdoor, daily wear—fashionable &amp; versatile, ideal for casual, sports &amp; sun protection. Popular overseas styles, abundant selections.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hats</t>
+          <t>Mise</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hats</t>
+          <t>mise</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>帽子作为四季必备的时尚配饰，兼具实用与装饰功能。从棒球帽、渔夫帽到贝雷帽、宽檐帽，多种款式满足不同场合与造型需求。选用棉、麻、羊毛等优质材料，兼顾舒适与风格。无论是遮阳防晒还是提升穿搭层次感，都是理想选择。探索经典与流行设计，搭配你的个性风格。</t>
+          <t>Mise 品类聚焦专业厨房预处理工具，适配海外餐饮从业者食材分拣、预处理需求，符合西餐 mise en place 操作标准，提升备餐效率，是海外厨师常用的厨房设备分类。</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hats &amp; Caps: Style &amp; Protection. Shop baseball caps, bucket hats, berets &amp; wide-brims. Made from cotton, wool &amp; more. Perfect for sun protection &amp; elevating any outfit. Explore classic &amp; trendy designs now! 🔍🧢☀️</t>
+          <t>MiseMise: Professional Kitchen Prep Tools for Overseas F&amp;B Pros. Tailored for food sorting &amp; prep needs, aligns with Western mise en place standards to boost meal prep efficiency— a common kitchen equipment category for overseas chefs.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mise</t>
+          <t>Toys</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mise</t>
+          <t>toys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mise作为专业厨房工具品牌，提供高品质刀具、锅具及烹饪配件，满足现代厨房的精准需求。我们的产品设计精巧、耐用安全，旨在提升烹饪效率与乐趣，是家庭主厨和料理爱好者的信赖之选。探索Mise，开启专业级烹饪体验。</t>
+          <t>玩具品类涵盖益智积木、毛绒玩偶、早教玩具等，符合欧美安全标准，适配0-12岁儿童，是节日礼物、日常玩乐优选，海外用户可放心选购。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mise: Professional knives, cookware &amp; kitchen tools. Precision-crafted, durable &amp; safe. Elevate your cooking efficiency &amp; joy. Trusted by home chefs. Explore Mise for a pro-level experience.</t>
+          <t>Our Toys category includes educational building blocks, plush dolls, and early education toys. Complying with EU &amp; US safety standards, they’re suitable for kids aged 0-12. Perfect for holiday gifts &amp; daily play—overseas buyers can shop confidently!</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Toys</t>
+          <t>‌Underwear</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>toys</t>
+          <t>underwear</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>玩具品类涵盖益智积木、毛绒玩偶、户外玩具、派对装饰等，适配0-12岁儿童。均符合ASTM、CE安全认证，满足节日送礼、日常玩耍、早教启蒙需求，安全耐玩。</t>
+          <t>Underwear（内衣裤）涵盖男士、女士、儿童款，主打舒适透气、棉质亲肤，含平角裤、三角裤等常见款式，贴合海外用户日常穿着需求，是谷歌等海外搜索平台热门品类。</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Engaging Kids Toys for 0-12 Years: Educational Building Blocks, Plush Dolls, Outdoor Toys, Party Decorations. ASTM &amp; CE Certified. Ideal for Holiday Gifting, Daily Play &amp; Early Education—Safe, Durable &amp; Fun!</t>
+          <t>Underwear for Men, Women &amp; Kids | Skin-friendly cotton, comfortable &amp; breathable. Includes popular styles (boxers, briefs) to meet overseas users’ daily wear needs. A top category on Google, Bing, Yahoo etc.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>‌Underwear</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>underwear</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>这个品类下，我们梳理了全球范围内的内衣系列，包络各种材质的内衣、保暖内衣、男女内衣，涵盖尽量多的品牌，名牌和潮流品牌，不同的款式、功能和季节等不同选择因素。总之，在内衣表单内，尽量微腻提供品有价廉的贴心选择。</t>
+          <t>其他未分类商品：涵盖未纳入主品类的各类实用好物，如家居小物、数码配件等，满足多样化需求，品质可靠，适配海外用户搜索习惯，便于快速查找所需商品。</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Discover affordable &amp; quality underwear! Explore a wide range of men's &amp; women's underwear, thermal wear, and styles for every season. Find your perfect fit now!</t>
+          <t>Other Unclassified Products: Covers practical items not in main categories (e.g., small home goods, digital accessories). Meets diverse needs with reliable quality, tailored to overseas users' search habits for quick access to desired products.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Glasses</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>glasses</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>我们提供多种优质电子配件，包括充电器、数据线、移动电源等，兼容主流品牌。精选材质，安全耐用，满足你的日常充电与数据传输需求。购物无忧，全球配送，售后完善。</t>
+          <t>眼镜品类含光学镜、太阳镜、蓝光眼镜，适配日常通勤、运动户外、办公护眼。主打防紫外线、抗蓝光疲劳、高清镜片，支持度数定制，满足近视、远视及无度数需求。</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Discover premium electronic accessories: chargers, cables, power banks. Compatible with major brands. Durable &amp; safe materials. Global shipping &amp; support. Shop now!</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Glasses</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>时尚眼镜，兼具视力矫正与潮流配饰功能。提供近视镜、太阳镜、老花镜及防蓝光护目镜。采用轻质材质与人体工学设计，全天候舒适佩戴。适合商务、休闲、驾驶等多场景，提升视觉清晰度与个人风格。全球品牌，品质保证。</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Glasses: Trendy eyewear for vision correction &amp; style. Featuring prescription, sunglasses, readers &amp; blue-light blocking. Lightweight &amp; ergonomic for all-day comfort. Ideal for work, leisure &amp; driving. Global brands. Shop now!</t>
+          <t>Our Glasses collection includes Optical Glasses, Sunglasses &amp; Blue Light Glasses—ideal for daily commute, sports/outdoor, office eye protection. Features UV protection, blue light anti-fatigue, HD lenses. Prescription customization available: fits myopia, hyperopia, non-prescription needs.</t>
         </is>
       </c>
     </row>
